--- a/MAJSushiConfig/ig/StructureDefinition-fr-patient-ins-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-patient-ins-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2633,7 +2633,7 @@
     <t>Patient.contact.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-human-name-document|0.1.0}
+    <t xml:space="preserve">HumanName {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-human-name-document|0.1.0}
 </t>
   </si>
   <si>
@@ -2823,7 +2823,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitioner-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0)
 </t>
   </si>
   <si>
@@ -3256,7 +3256,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="98.9765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="95.77734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
